--- a/verificables revisión sistemática/S4_pre_extraccion_desde_resumen.xlsx
+++ b/verificables revisión sistemática/S4_pre_extraccion_desde_resumen.xlsx
@@ -881,7 +881,7 @@
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-08-26</t>
+          <t>Generado el 2026-08-28</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S4_pre_extraccion_desde_resumen.xlsx
+++ b/verificables revisión sistemática/S4_pre_extraccion_desde_resumen.xlsx
@@ -881,7 +881,7 @@
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-08-28</t>
+          <t>Generado el 2026-08-31</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S4_pre_extraccion_desde_resumen.xlsx
+++ b/verificables revisión sistemática/S4_pre_extraccion_desde_resumen.xlsx
@@ -881,7 +881,7 @@
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-08-31</t>
+          <t>Generado el 2026-09-01</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S4_pre_extraccion_desde_resumen.xlsx
+++ b/verificables revisión sistemática/S4_pre_extraccion_desde_resumen.xlsx
@@ -2658,7 +2658,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -3808,7 +3808,7 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -4201,7 +4201,7 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5755,7 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -7108,7 +7108,7 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -7270,7 +7270,7 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -7724,7 +7724,7 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -8218,7 +8218,7 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -9255,7 +9255,7 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -9595,7 +9595,7 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -9883,7 +9883,7 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -11172,7 +11172,7 @@
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -12270,7 +12270,7 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -12732,7 +12732,7 @@
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -13421,7 +13421,7 @@
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -13705,7 +13705,7 @@
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -13879,7 +13879,7 @@
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S4_pre_extraccion_desde_resumen.xlsx
+++ b/verificables revisión sistemática/S4_pre_extraccion_desde_resumen.xlsx
@@ -7659,7 +7659,7 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -8295,7 +8295,7 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -10864,7 +10864,7 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -13956,7 +13956,7 @@
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S4_pre_extraccion_desde_resumen.xlsx
+++ b/verificables revisión sistemática/S4_pre_extraccion_desde_resumen.xlsx
@@ -881,7 +881,7 @@
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-01</t>
+          <t>Generado el 2026-09-02</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S4_pre_extraccion_desde_resumen.xlsx
+++ b/verificables revisión sistemática/S4_pre_extraccion_desde_resumen.xlsx
@@ -12193,7 +12193,7 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S4_pre_extraccion_desde_resumen.xlsx
+++ b/verificables revisión sistemática/S4_pre_extraccion_desde_resumen.xlsx
@@ -9036,7 +9036,7 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -13559,7 +13559,7 @@
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S4_pre_extraccion_desde_resumen.xlsx
+++ b/verificables revisión sistemática/S4_pre_extraccion_desde_resumen.xlsx
@@ -881,7 +881,7 @@
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-02</t>
+          <t>Generado el 2026-09-14</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S4_pre_extraccion_desde_resumen.xlsx
+++ b/verificables revisión sistemática/S4_pre_extraccion_desde_resumen.xlsx
@@ -881,7 +881,7 @@
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-14</t>
+          <t>Generado el 2026-09-15</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S4_pre_extraccion_desde_resumen.xlsx
+++ b/verificables revisión sistemática/S4_pre_extraccion_desde_resumen.xlsx
@@ -881,7 +881,7 @@
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-15</t>
+          <t>Generado el 2026-09-16</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S4_pre_extraccion_desde_resumen.xlsx
+++ b/verificables revisión sistemática/S4_pre_extraccion_desde_resumen.xlsx
@@ -881,7 +881,7 @@
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-16</t>
+          <t>Generado el 2026-09-22</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S4_pre_extraccion_desde_resumen.xlsx
+++ b/verificables revisión sistemática/S4_pre_extraccion_desde_resumen.xlsx
@@ -6010,7 +6010,7 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S4_pre_extraccion_desde_resumen.xlsx
+++ b/verificables revisión sistemática/S4_pre_extraccion_desde_resumen.xlsx
@@ -881,7 +881,7 @@
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-22</t>
+          <t>Generado el 2026-09-23</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S4_pre_extraccion_desde_resumen.xlsx
+++ b/verificables revisión sistemática/S4_pre_extraccion_desde_resumen.xlsx
@@ -881,7 +881,7 @@
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-23</t>
+          <t>Generado el 2026-10-03</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -5431,7 +5431,7 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -12509,7 +12509,7 @@
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -13794,7 +13794,7 @@
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S4_pre_extraccion_desde_resumen.xlsx
+++ b/verificables revisión sistemática/S4_pre_extraccion_desde_resumen.xlsx
@@ -881,7 +881,7 @@
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-03</t>
+          <t>Generado el 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -4533,7 +4533,7 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -5690,7 +5690,7 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -10041,7 +10041,7 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -11877,7 +11877,7 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S4_pre_extraccion_desde_resumen.xlsx
+++ b/verificables revisión sistemática/S4_pre_extraccion_desde_resumen.xlsx
@@ -881,7 +881,7 @@
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-06</t>
+          <t>Generado el 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -3585,7 +3585,7 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3650,7 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -5358,7 +5358,7 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -6075,7 +6075,7 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -6399,7 +6399,7 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -6808,7 +6808,7 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -8060,7 +8060,7 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -8724,7 +8724,7 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -8801,7 +8801,7 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -10491,7 +10491,7 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -11411,7 +11411,7 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -11565,7 +11565,7 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -12801,7 +12801,7 @@
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>si</t>
+          <t>no</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S4_pre_extraccion_desde_resumen.xlsx
+++ b/verificables revisión sistemática/S4_pre_extraccion_desde_resumen.xlsx
@@ -499,7 +499,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>La pre-extracción desde el resumen, que es la fuente de TODA cifra que el artículo publica.</t>
+          <t>La pre-extracción desde el resumen, emitida por el modelo de lenguaje (Claude Opus 5); fuente de las cifras estructurales (secciones 3.1 a 3.4).</t>
         </is>
       </c>
     </row>
@@ -516,7 +516,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Sección 2.6. Cada fila va marcada PARCIAL: describe lo que el resumen declara, no el texto completo.</t>
+          <t>Sección 2.6. Cada fila va marcada PARCIAL: describe lo que el resumen declara, no el texto completo. Los desenlaces (sección 3.5, tabla 5) salen de la extracción adjudicada, S14.</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-07</t>
+          <t>Generado el 2026-10-12</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S4_pre_extraccion_desde_resumen.xlsx
+++ b/verificables revisión sistemática/S4_pre_extraccion_desde_resumen.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,6 +41,10 @@
       <b val="1"/>
       <color rgb="001F4E79"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -89,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -100,11 +104,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -472,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -521,367 +528,374 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Las secciones y tablas que se citan son las del informe extendido (manuscrito maestro). En el manuscrito preparado para la revista las secciones no van numeradas; allí la tabla 5 (desenlaces) es la Tabla 4.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Cuántas filas</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>159 filas de datos</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
-    </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Qué significa cada columna</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Identificador del estudio</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>columna interna: id_provisional</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Brazo</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>columna interna: arm_id</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>¿Solo P. aeruginosa o mixto?</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>columna interna: pathogen_scope</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>Clase de resistencia</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>columna interna: resistance_class</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>De dónde sale la clase</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>columna interna: resistance_class_source</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>¿Cumple criterio DTR?</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>columna interna: dtr_status</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>Vía de administración</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>columna interna: route</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>¿Fago solo o con antibiótico?</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>columna interna: modality</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>Diseño del estudio</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>columna interna: study_design</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>Estado de la extracción</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>columna interna: extraction_status</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>Pacientes en el brazo</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>columna interna: n_arm</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>clinical_success_n</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>columna interna: clinical_success_n</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>adverse_event_n</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>columna interna: adverse_event_n</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>microbio_eradication_n</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>columna interna: microbio_eradication_n</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>mortality_n</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>columna interna: mortality_n</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>los_days</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>columna interna: los_days</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>resistance_emergence_n</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>columna interna: resistance_emergence_n</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>publication_year</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>columna interna: publication_year</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>clinical_success_definition</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>columna interna: clinical_success_definition</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>journal_tier</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>columna interna: journal_tier</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>geographic_source</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>columna interna: geographic_source</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>extraction_citation</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>columna interna: extraction_citation</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>incomplete_reason</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>columna interna: incomplete_reason</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>alerta_microbiologia</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>columna interna: alerta_microbiologia</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>alerta_revision</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>columna interna: alerta_revision</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>registrado_en</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>columna interna: registrado_en</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>¿Sigue en el corpus?</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>columna interna: en_corpus_actual</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
         <is>
           <t>El CSV con los nombres internos acompaña a este fichero: es la copia reproducible.</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="7" t="inlineStr">
-        <is>
-          <t>Generado el 2026-10-12</t>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>Generado el 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -929,137 +943,137 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Identificador del estudio</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>Brazo</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>¿Solo P. aeruginosa o mixto?</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>Clase de resistencia</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>De dónde sale la clase</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>¿Cumple criterio DTR?</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>Vía de administración</t>
         </is>
       </c>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>¿Fago solo o con antibiótico?</t>
         </is>
       </c>
-      <c r="I1" s="8" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>Diseño del estudio</t>
         </is>
       </c>
-      <c r="J1" s="8" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>Estado de la extracción</t>
         </is>
       </c>
-      <c r="K1" s="8" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>Pacientes en el brazo</t>
         </is>
       </c>
-      <c r="L1" s="8" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>clinical_success_n</t>
         </is>
       </c>
-      <c r="M1" s="8" t="inlineStr">
+      <c r="M1" s="9" t="inlineStr">
         <is>
           <t>adverse_event_n</t>
         </is>
       </c>
-      <c r="N1" s="8" t="inlineStr">
+      <c r="N1" s="9" t="inlineStr">
         <is>
           <t>microbio_eradication_n</t>
         </is>
       </c>
-      <c r="O1" s="8" t="inlineStr">
+      <c r="O1" s="9" t="inlineStr">
         <is>
           <t>mortality_n</t>
         </is>
       </c>
-      <c r="P1" s="8" t="inlineStr">
+      <c r="P1" s="9" t="inlineStr">
         <is>
           <t>los_days</t>
         </is>
       </c>
-      <c r="Q1" s="8" t="inlineStr">
+      <c r="Q1" s="9" t="inlineStr">
         <is>
           <t>resistance_emergence_n</t>
         </is>
       </c>
-      <c r="R1" s="8" t="inlineStr">
+      <c r="R1" s="9" t="inlineStr">
         <is>
           <t>publication_year</t>
         </is>
       </c>
-      <c r="S1" s="8" t="inlineStr">
+      <c r="S1" s="9" t="inlineStr">
         <is>
           <t>clinical_success_definition</t>
         </is>
       </c>
-      <c r="T1" s="8" t="inlineStr">
+      <c r="T1" s="9" t="inlineStr">
         <is>
           <t>journal_tier</t>
         </is>
       </c>
-      <c r="U1" s="8" t="inlineStr">
+      <c r="U1" s="9" t="inlineStr">
         <is>
           <t>geographic_source</t>
         </is>
       </c>
-      <c r="V1" s="8" t="inlineStr">
+      <c r="V1" s="9" t="inlineStr">
         <is>
           <t>extraction_citation</t>
         </is>
       </c>
-      <c r="W1" s="8" t="inlineStr">
+      <c r="W1" s="9" t="inlineStr">
         <is>
           <t>incomplete_reason</t>
         </is>
       </c>
-      <c r="X1" s="8" t="inlineStr">
+      <c r="X1" s="9" t="inlineStr">
         <is>
           <t>alerta_microbiologia</t>
         </is>
       </c>
-      <c r="Y1" s="8" t="inlineStr">
+      <c r="Y1" s="9" t="inlineStr">
         <is>
           <t>alerta_revision</t>
         </is>
       </c>
-      <c r="Z1" s="8" t="inlineStr">
+      <c r="Z1" s="9" t="inlineStr">
         <is>
           <t>registrado_en</t>
         </is>
       </c>
-      <c r="AA1" s="8" t="inlineStr">
+      <c r="AA1" s="9" t="inlineStr">
         <is>
           <t>¿Sigue en el corpus?</t>
         </is>

--- a/verificables revisión sistemática/S4_pre_extraccion_desde_resumen.xlsx
+++ b/verificables revisión sistemática/S4_pre_extraccion_desde_resumen.xlsx
@@ -895,7 +895,7 @@
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-14</t>
+          <t>Generado el 2026-10-15</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S4_pre_extraccion_desde_resumen.xlsx
+++ b/verificables revisión sistemática/S4_pre_extraccion_desde_resumen.xlsx
@@ -895,7 +895,7 @@
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-15</t>
+          <t>Generado el 2026-10-19</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S4_pre_extraccion_desde_resumen.xlsx
+++ b/verificables revisión sistemática/S4_pre_extraccion_desde_resumen.xlsx
@@ -696,7 +696,7 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>clinical_success_n</t>
+          <t>Éxito clínico (nº pacientes)</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
@@ -708,7 +708,7 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>adverse_event_n</t>
+          <t>Eventos adversos (nº)</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
@@ -720,7 +720,7 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>microbio_eradication_n</t>
+          <t>Erradicación microbiológica (nº)</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
@@ -732,7 +732,7 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>mortality_n</t>
+          <t>Fallecidos (nº)</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -744,7 +744,7 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>los_days</t>
+          <t>Estancia hospitalaria (días)</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
@@ -756,7 +756,7 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>resistance_emergence_n</t>
+          <t>Aparición de resistencia al fago (nº)</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
@@ -768,7 +768,7 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>publication_year</t>
+          <t>Año de publicación</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -780,7 +780,7 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>clinical_success_definition</t>
+          <t>¿Cómo define el AUTOR el éxito clínico?</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
@@ -792,7 +792,7 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>journal_tier</t>
+          <t>Nivel de la revista</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
@@ -804,7 +804,7 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>geographic_source</t>
+          <t>País del estudio</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
@@ -816,7 +816,7 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>extraction_citation</t>
+          <t>¿Dónde viste estos datos?</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
@@ -828,7 +828,7 @@
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>incomplete_reason</t>
+          <t>Si algo quedó incompleto, ¿por qué?</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
@@ -1000,62 +1000,62 @@
       </c>
       <c r="L1" s="9" t="inlineStr">
         <is>
-          <t>clinical_success_n</t>
+          <t>Éxito clínico (nº pacientes)</t>
         </is>
       </c>
       <c r="M1" s="9" t="inlineStr">
         <is>
-          <t>adverse_event_n</t>
+          <t>Eventos adversos (nº)</t>
         </is>
       </c>
       <c r="N1" s="9" t="inlineStr">
         <is>
-          <t>microbio_eradication_n</t>
+          <t>Erradicación microbiológica (nº)</t>
         </is>
       </c>
       <c r="O1" s="9" t="inlineStr">
         <is>
-          <t>mortality_n</t>
+          <t>Fallecidos (nº)</t>
         </is>
       </c>
       <c r="P1" s="9" t="inlineStr">
         <is>
-          <t>los_days</t>
+          <t>Estancia hospitalaria (días)</t>
         </is>
       </c>
       <c r="Q1" s="9" t="inlineStr">
         <is>
-          <t>resistance_emergence_n</t>
+          <t>Aparición de resistencia al fago (nº)</t>
         </is>
       </c>
       <c r="R1" s="9" t="inlineStr">
         <is>
-          <t>publication_year</t>
+          <t>Año de publicación</t>
         </is>
       </c>
       <c r="S1" s="9" t="inlineStr">
         <is>
-          <t>clinical_success_definition</t>
+          <t>¿Cómo define el AUTOR el éxito clínico?</t>
         </is>
       </c>
       <c r="T1" s="9" t="inlineStr">
         <is>
-          <t>journal_tier</t>
+          <t>Nivel de la revista</t>
         </is>
       </c>
       <c r="U1" s="9" t="inlineStr">
         <is>
-          <t>geographic_source</t>
+          <t>País del estudio</t>
         </is>
       </c>
       <c r="V1" s="9" t="inlineStr">
         <is>
-          <t>extraction_citation</t>
+          <t>¿Dónde viste estos datos?</t>
         </is>
       </c>
       <c r="W1" s="9" t="inlineStr">
         <is>
-          <t>incomplete_reason</t>
+          <t>Si algo quedó incompleto, ¿por qué?</t>
         </is>
       </c>
       <c r="X1" s="9" t="inlineStr">

--- a/verificables revisión sistemática/S4_pre_extraccion_desde_resumen.xlsx
+++ b/verificables revisión sistemática/S4_pre_extraccion_desde_resumen.xlsx
@@ -895,7 +895,7 @@
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-19</t>
+          <t>Generado el 2026-10-20</t>
         </is>
       </c>
     </row>
